--- a/rsg2030/eingaben/2026/freigabe.xlsx
+++ b/rsg2030/eingaben/2026/freigabe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxplischke/Developer/GitHub/rsg-2030-verordnungen/rsg2030/eingaben/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BDB9CF-3C9D-D346-B80B-65FB53CB3550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAAEAF0-3FCE-9E44-BED6-91BCEB940A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="60160" windowHeight="31080" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="60160" windowHeight="31080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Bildseiten!$A$2:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Entscheidungen!$A$2:$M$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Entscheidungen!$A$2:$M$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Fußnoten!$A$2:$I$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Spalten!$A$2:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Zeilen!$A$2:$J$30</definedName>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="868">
   <si>
     <t>Freigabe RSG 2030 – was ein Mensch am PDF bestätigt</t>
   </si>
@@ -897,7 +897,7 @@
     <t>korrekturen.csv, Art «Fußnote» (KFO); METHODIK.md R4 «ZMK und KFO je Land»</t>
   </si>
   <si>
-    <t>KFO-ÄAVE aus der Fußnote in ZMK übernommen; Planstellen nicht; «exkl.» Notdienstzentrum Linz und Vorgriffstelle Steyr nicht beziffert, nicht ergänzt (METHODIK R4)</t>
+    <t>KFO-ÄAVE und KFO-Planstellen aus der Fußnote übernommen (Planstellen: IST je Träger, PLAN gemeinsame Sachleistungsstellen mit 100 % Maximalanteil); «exkl.» Notdienstzentrum Linz und Vorgriffstelle Steyr nicht beziffert, nicht ergänzt (METHODIK R4)</t>
   </si>
   <si>
     <t>OÖ BL S.10 *ZMK</t>
@@ -930,7 +930,7 @@
     <t>exkl. zahnärztliches Notdienstzentrum Linz; zusätzlich KFO: IST 2022 und Plan 2030: 11,5 ÄAVE bzw. 9 vertragskieferorthopädische Planstellen SV; Im Gesamtvertrag der SVS mit der Zahnärztekammer ist derzeit kein Stellenplan vereinbart. Jeder zur selbständigen Berufsausübung berechtigter Zahnarzt kann mittels Verpflichtungserklärung eine Direktverrechnung mit der SVS durchführen.</t>
   </si>
   <si>
-    <t>KFO-ÄAVE aus der Fußnote in ZMK übernommen; Planstellen nicht; «exkl.» Notdienstzentrum Linz nicht beziffert, nicht ergänzt (METHODIK R4)</t>
+    <t>KFO-ÄAVE und KFO-Planstellen aus der Fußnote übernommen (Planstellen: IST je Träger, PLAN gemeinsame Sachleistungsstellen mit 100 % Maximalanteil); «exkl.» Notdienstzentrum Linz nicht beziffert, nicht ergänzt (METHODIK R4)</t>
   </si>
   <si>
     <t>OÖ VR 41 S.12 *ZMK</t>
@@ -945,7 +945,7 @@
     <t>zusätzlich KFO: IST 2022 und Plan 2030: 3,3 ÄAVE bzw. 5 vertragskieferorthopädische Planstellen SV; Im Gesamtvertrag der SVS mit der Zahnärztekammer ist derzeit kein Stellenplan vereinbart. Jeder zur selbständigen Berufsausübung berechtigter Zahnarzt kann mittels Verpflichtungserklärung eine Direktverrechnung mit der SVS durchführen.</t>
   </si>
   <si>
-    <t>KFO-ÄAVE aus der Fußnote in ZMK übernommen; Planstellen nicht</t>
+    <t>KFO-ÄAVE und KFO-Planstellen aus der Fußnote übernommen (Planstellen: IST je Träger, PLAN gemeinsame Sachleistungsstellen mit 100 % Maximalanteil)</t>
   </si>
   <si>
     <t>OÖ VR 42 S.15 *ZMK</t>
@@ -972,7 +972,7 @@
     <t>exkl. einer Vorgriffstelle in Steyr; zusätzlich KFO: IST 2022 und Plan 2030: 5,8 ÄAVE bzw. 3 vertragskieferorthopädische Planstellen SV; Im Gesamtvertrag der SVS mit der Zahnärztekammer ist derzeit kein Stellenplan vereinbart. Jeder zur selbständigen Berufsausübung berechtigter Zahnarzt kann mittels Verpflichtungserklärung eine Direktverrechnung mit der SVS durchführen.</t>
   </si>
   <si>
-    <t>KFO-ÄAVE aus der Fußnote in ZMK übernommen; Planstellen nicht; «exkl.» Vorgriffstelle Steyr nicht beziffert, nicht ergänzt (METHODIK R4)</t>
+    <t>KFO-ÄAVE und KFO-Planstellen aus der Fußnote übernommen (Planstellen: IST je Träger, PLAN gemeinsame Sachleistungsstellen mit 100 % Maximalanteil); «exkl.» Vorgriffstelle Steyr nicht beziffert, nicht ergänzt (METHODIK R4)</t>
   </si>
   <si>
     <t>OÖ VR 44 S.21 *ZMK</t>
@@ -2061,13 +2061,13 @@
 BL IST niedergelassen KFO: (leer) → 38,2</t>
   </si>
   <si>
-    <t>PDF S.10, Fußnote zu «ZMK*» (OÖ gesamt): «ZMK – exkl. …; zusätzlich KFO: IST 2022 und Plan 2030: 38,2 ÄAVE bzw. 32 vertragskieferorthopädische Planstellen SV». Matrix ohne KFO-Spalte, ZMK und gesamt ohne KFO. Gelesen als: 38,2 ÄAVE in IST und PLAN; zugeordnet zu insgesamt und zur Zeile der Niedergelassenen (IST niedergelassen, PLAN niedergelassen+Ambulatorien), gesamt + 38,2. Planstellen nicht übernommen (Träger nicht angegeben)</t>
+    <t>PDF S.10, Fußnote zu «ZMK*» (OÖ gesamt): «ZMK – exkl. …; zusätzlich KFO: IST 2022 und Plan 2030: 38,2 ÄAVE bzw. 32 vertragskieferorthopädische Planstellen SV». Matrix ohne KFO-Spalte, ZMK und gesamt ohne KFO. Gelesen als: 38,2 ÄAVE in IST und PLAN; zugeordnet zu insgesamt und zur Zeile der Niedergelassenen (IST niedergelassen, PLAN niedergelassen+Ambulatorien), gesamt + 38,2. Die 32 Planstellen stehen in eigenen Regeln (Zeilen planstellen_oegk/_svs/_bvaeb und slst_gemeinsam). Nicht doppelt: Das Monitoring führt ZMK inkl. KFO und passt erst mit den Fußnotenzahlen (PRUEFUNG.md, «Steckt KFO schon in der gedruckten ZMK-Spalte?»)</t>
   </si>
   <si>
     <t>K|OÖ|BL|OÖ|haupt|*|insgesamt+niedergelassen+extramural|KFO|zusatz:38.2</t>
   </si>
   <si>
-    <t>8288d6dcadd7</t>
+    <t>76f3b3729afe</t>
   </si>
   <si>
     <t>OÖ · VR 41 · haupt · *</t>
@@ -2196,18 +2196,249 @@
     <t>46f02c9085c2</t>
   </si>
   <si>
+    <t>ÖGK - Planstellen · SVS - Planstellen · BVAEB - Planstellen · Gemeinsame Sachleistungsstellen aller KV-Träger</t>
+  </si>
+  <si>
+    <t>planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam</t>
+  </si>
+  <si>
+    <t>zusatz:32</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+BL IST planstellen_oegk KFO: (leer) → 32
+BL IST planstellen_oegk gesamt: 1520,1 → 1552,1
+BL IST planstellen_svs KFO: (leer) → 32</t>
+  </si>
+  <si>
+    <t>PDF S.10, Fußnote zu «ZMK*» (OÖ gesamt): «… zusätzlich KFO: IST 2022 und Plan 2030: 38,2 ÄAVE bzw. 32 vertragskieferorthopädische Planstellen SV». Derselbe Satz gilt für IST und PLAN, wie bei den ÄAVE (Regel zusatz:38.2). IST: in jede Träger-Zeile 32 – die Bezirksseiten derselben Anlage (S.13, 16, 19, 22, 25, 28) nennen die Träger selbst: «ZMK – zuzügl. in Kieferorthopädie (KFO): n vertragskieferorthopädische Planstellen: ÖGK, SVS, BVAEB», für jeden der 18 Bezirke, je Seite die Zahl der VR-Fußnote und zusammen 32; «zuzügl.» steht dort neben «davon in Unfallchirurgie (UC)», die Verordnung trennt also zusätzlich von enthalten. Ebenso in allen sechs Ländern mit eigener KFO-Spalte, auch wo ZMK bei der SVS «-» ist (Steiermark S.1: ZMK «-», KFO 25). PLAN: in die gemeinsamen Sachleistungsstellen, weil «SV» ohne Träger die Stellen aller Träger meint und die sechs Länder KFO dort vollständig führen (zusätzliche je Träger überall 0). «gesamt» der Zeilen + 32. Stützt die Lesart: RSG-Monitoring, ÖGK-Planstellen ZMK inkl. KFO 414 gegenüber gedruckt 381, mit den 32 nun 413; in den übrigen Ländern mit KFO-Spalte passt gedruckt + KFO genauso erst zusammen (PRUEFUNG.md, «Steckt KFO schon in der gedruckten ZMK-Spalte?»). Nicht bestätigt: offene_punkte.md «Oberösterreich»</t>
+  </si>
+  <si>
+    <t>K|OÖ|BL|OÖ|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:32</t>
+  </si>
+  <si>
+    <t>9158af7cac87</t>
+  </si>
+  <si>
+    <t>zusatz:9</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 41 IST planstellen_oegk KFO: (leer) → 9
+VR 41 IST planstellen_oegk gesamt: 415,7 → 424,7
+VR 41 IST planstellen_svs KFO: (leer) → 9</t>
+  </si>
+  <si>
+    <t>PDF S.12, Fußnote VR 41 zu «ZMK*»: «… bzw. 9 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|41|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:9</t>
+  </si>
+  <si>
+    <t>7047eb1818fe</t>
+  </si>
+  <si>
+    <t>zusatz:5</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 42 IST planstellen_oegk KFO: (leer) → 5
+VR 42 IST planstellen_oegk gesamt: 241 → 246
+VR 42 IST planstellen_svs KFO: (leer) → 5</t>
+  </si>
+  <si>
+    <t>PDF S.15, Fußnote VR 42 zu «ZMK*»: «… bzw. 5 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|42|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:5</t>
+  </si>
+  <si>
+    <t>aba8babcdebb</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 43 IST planstellen_oegk KFO: (leer) → 5
+VR 43 IST planstellen_oegk gesamt: 242,9 → 247,9
+VR 43 IST planstellen_svs KFO: (leer) → 5</t>
+  </si>
+  <si>
+    <t>PDF S.18, Fußnote VR 43 zu «ZMK*»: «… bzw. 5 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|43|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:5</t>
+  </si>
+  <si>
+    <t>66c9129f556c</t>
+  </si>
+  <si>
+    <t>zusatz:3</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 44 IST planstellen_oegk KFO: (leer) → 3
+VR 44 IST planstellen_oegk gesamt: 165,2 → 168,2
+VR 44 IST planstellen_svs KFO: (leer) → 3</t>
+  </si>
+  <si>
+    <t>PDF S.21, Fußnote VR 44 zu «ZMK*»: «… bzw. 3 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|44|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:3</t>
+  </si>
+  <si>
+    <t>b9f431326f40</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 45 IST planstellen_oegk KFO: (leer) → 5
+VR 45 IST planstellen_oegk gesamt: 244,7 → 249,7
+VR 45 IST planstellen_svs KFO: (leer) → 5</t>
+  </si>
+  <si>
+    <t>PDF S.24, Fußnote VR 45 zu «ZMK*»: «… bzw. 5 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|45|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:5</t>
+  </si>
+  <si>
+    <t>5a336ddf2ca2</t>
+  </si>
+  <si>
+    <t>8 Zellen, z. B.
+VR 46 IST planstellen_oegk KFO: (leer) → 5
+VR 46 IST planstellen_oegk gesamt: 210,6 → 215,6
+VR 46 IST planstellen_svs KFO: (leer) → 5</t>
+  </si>
+  <si>
+    <t>PDF S.27, Fußnote VR 46 zu ZMK (Spaltenkopf ohne Stern): «… bzw. 5 vertragskieferorthopädische Planstellen SV»; Zuordnung wie BL (S.10). Die sechs VR ergeben zusammen 32 = Bundesland; dieselbe Zahl ergeben die Bezirke der VR auf der folgenden Bezirksseite («zuzügl. in Kieferorthopädie (KFO): … ÖGK, SVS, BVAEB»)</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|46|haupt|*|planstellen_oegk+planstellen_svs+planstellen_bvaeb+slst_gemeinsam|KFO|zusatz:5</t>
+  </si>
+  <si>
+    <t>1e210c340a3d</t>
+  </si>
+  <si>
+    <t>OÖ · BL OÖ · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>Gemeinsame Sachleistungsstellen aller KV-Träger [Zeile nicht im PDF] – zu: «Gemeinsame Sachleistungsstellen aller KV-Träger»</t>
+  </si>
+  <si>
+    <t>slst_gemeinsam_max_vaep_prozent</t>
+  </si>
+  <si>
+    <t>wert:100</t>
+  </si>
+  <si>
+    <t>BL KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.10: Die Fußnote nennt «32 vertragskieferorthopädische Planstellen SV»; Planstellen sind der vertragsärztliche Teil der Sachleistungsstellen (Tabellenband S.252), der Maximalanteil also 100 %. Ein %-Feld gibt es nicht, weil KFO in OÖ keine Spalte hat. Die sechs Länder mit KFO-Spalte drucken 75–100 % (Bgld 100, Ktn 100, NÖ 94,8, Sbg 75, Stmk 96, Tirol 96). Lesart aus dem Wortlaut, keine Herleitung aus dem Dokument; offene_punkte.md «Oberösterreich»</t>
+  </si>
+  <si>
+    <t>K|OÖ|BL|OÖ|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>2ae6705212ed</t>
+  </si>
+  <si>
+    <t>OÖ · VR 41 · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>VR 41 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.12 (VR 41): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|41|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>75e178fdcc04</t>
+  </si>
+  <si>
     <t>OÖ · VR 42 · haupt · PLAN</t>
   </si>
   <si>
+    <t>VR 42 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.15 (VR 42): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|42|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>c7248a9c37c2</t>
+  </si>
+  <si>
+    <t>OÖ · VR 43 · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>VR 43 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.18 (VR 43): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|43|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>6da7c44f9e6b</t>
+  </si>
+  <si>
+    <t>OÖ · VR 44 · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>VR 44 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.21 (VR 44): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|44|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>fe4e8a8b3aeb</t>
+  </si>
+  <si>
+    <t>OÖ · VR 45 · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>VR 45 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.24 (VR 45): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|45|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>1c5e31d100da</t>
+  </si>
+  <si>
+    <t>OÖ · VR 46 · haupt · PLAN</t>
+  </si>
+  <si>
+    <t>VR 46 KFO: (leer) → 100</t>
+  </si>
+  <si>
+    <t>PDF S.27 (VR 46): 100 % wie im Bundesland (S.10), gleicher Wortlaut der Fußnote</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|46|haupt|PLAN|slst_gemeinsam_max_vaep_prozent|KFO|wert:100</t>
+  </si>
+  <si>
+    <t>b68d3e899aad</t>
+  </si>
+  <si>
     <t>zusätzliche SVS-Sachleistungsstellen [Zeile nicht im PDF] – zu: «zusätzliche SVS-Sachleistungsstellen»</t>
   </si>
   <si>
     <t>slst_zus_svs_max_vaep_prozent</t>
   </si>
   <si>
-    <t>wert:100</t>
-  </si>
-  <si>
     <t>VR 42 IM: (leer) → 100</t>
   </si>
   <si>
@@ -2262,6 +2493,30 @@
     <t>f068f991f872</t>
   </si>
   <si>
+    <t>URO</t>
+  </si>
+  <si>
+    <t>wert:0</t>
+  </si>
+  <si>
+    <t>BL URO: (leer) → 0</t>
+  </si>
+  <si>
+    <t>PDF S.9 (BL) bzw. S.11 (VR 41): zusätzliche SVS-Sachleistungsstellen URO je 1,5, das %-Feld darunter leer – URO ist das einzige Fach dieser Zeile mit Stellen, aber ohne Maximalanteil, und der Wert folgt aus keiner anderen Zahl (BL = VR 41). Als Lesart 0 % gesetzt: 0 % ist in dieser Zeile der häufigste gedruckte Wert (BL 4 von 12 Fächern mit %, VR 41 6 von 12). Keine Herleitung – offene_punkte.md «Oberösterreich». Folge: das gesamt-% der Zeile wird dadurch abgeleitet (gewichtetes Mittel)</t>
+  </si>
+  <si>
+    <t>K|OÖ|BL|OÖ|haupt|PLAN|slst_zus_svs_max_vaep_prozent|URO|wert:0</t>
+  </si>
+  <si>
+    <t>95b826951dcc</t>
+  </si>
+  <si>
+    <t>VR 41 URO: (leer) → 0</t>
+  </si>
+  <si>
+    <t>K|OÖ|VR|41|haupt|PLAN|slst_zus_svs_max_vaep_prozent|URO|wert:0</t>
+  </si>
+  <si>
     <t>Kärnten · BL * · haupt · PLAN</t>
   </si>
   <si>
@@ -2278,9 +2533,6 @@
   </si>
   <si>
     <t>- davon maximal als vertragsärztliche Planstellen in % – zu: «Gemeinsame Sachleistungsstellen aller KV-Träger»</t>
-  </si>
-  <si>
-    <t>slst_gemeinsam_max_vaep_prozent</t>
   </si>
   <si>
     <t>VR 82 gesamt: 0 → (leer)</t>
@@ -2430,24 +2682,6 @@
     <t>9f02fb7d5bb8</t>
   </si>
   <si>
-    <t>OÖ · OÖ · haupt · PLAN</t>
-  </si>
-  <si>
-    <t>zusätzliche SVS-Sachleistungsstellen</t>
-  </si>
-  <si>
-    <t>URO</t>
-  </si>
-  <si>
-    <t>PDF S.9 (BL) und S.11 (VR 41, die einzige VR mit URO-Stellen): zusätzliche SVS-Sachleistungsstellen URO je 1,5, das %-Feld darunter leer – wie viel davon höchstens Kassenpraxis sein darf, steht nirgends und folgt aus keiner anderen Zahl (BL = VR 41); gesamt-% der Zeile daher nicht abgeleitet</t>
-  </si>
-  <si>
-    <t>B|prozent_gewichtet|OÖ|OÖ|haupt|PLAN|slst_zus_svs_max_vaep_prozent|URO</t>
-  </si>
-  <si>
-    <t>5782d3ca1744</t>
-  </si>
-  <si>
     <t>Burgenland · * · aequivalent · PLAN</t>
   </si>
   <si>
@@ -2555,7 +2789,7 @@
     <t>gewichtetes_mittel:fachspalten</t>
   </si>
   <si>
-    <t>64 Zellen in 26 Matrizen (Burgenland, Kärnten, OÖ, Steiermark, Vorarlberg, Wien)</t>
+    <t>66 Zellen in 26 Matrizen (Burgenland, Kärnten, OÖ, Steiermark, Vorarlberg, Wien)</t>
   </si>
   <si>
     <t>Das gesamt-% einer Zeile «- davon maximal als vertragsärztliche Planstellen in %» ist der Anteil aller Stellen der Zeile, der höchstens als Kassenpraxis besetzt werden darf: das mit den Stellen gewichtete Mittel der Fach-% (jedes gedruckte gesamt-% rechnet so, Prüfung prozent_gesamt). Die ÖSG-Vorlage sieht das Feld vor (Tabellenband S.259), viele Länder füllen es nicht aus. Abgeleitet nur, wo jedes Fach mit Stellen ein % hat.</t>
@@ -6645,7 +6879,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -7751,7 +7985,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="96" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>635</v>
       </c>
@@ -8066,102 +8300,102 @@
         <v>679</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" ht="192" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>504</v>
+        <v>635</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>680</v>
+        <v>636</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E33" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="H33" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I33" s="4" t="s">
+      <c r="J33" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="K33" s="5" t="s">
         <v>684</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>685</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M33" s="9"/>
       <c r="N33" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="O33" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="O33" s="4" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>504</v>
+        <v>635</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>680</v>
+        <v>644</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D34" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>682</v>
-      </c>
       <c r="H34" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="I34" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="J34" s="5" t="s">
+      <c r="K34" s="5" t="s">
         <v>689</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>690</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M34" s="9"/>
       <c r="N34" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="O34" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="O34" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>504</v>
+        <v>635</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>58</v>
@@ -8170,19 +8404,19 @@
         <v>14</v>
       </c>
       <c r="E35" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>682</v>
-      </c>
       <c r="H35" s="4" t="s">
-        <v>57</v>
+        <v>515</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>693</v>
@@ -8201,682 +8435,1365 @@
         <v>696</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>504</v>
+        <v>635</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D36" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E36" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>682</v>
-      </c>
       <c r="H36" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="J36" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="I36" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="J36" s="5" t="s">
+      <c r="K36" s="5" t="s">
         <v>698</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>699</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M36" s="9"/>
       <c r="N36" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="O36" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="O36" s="4" t="s">
+    </row>
+    <row r="37" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="4">
+        <v>20</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="B37" s="4" t="s">
+      <c r="J37" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="4">
-        <v>97</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="J37" s="5" t="s">
+      <c r="K37" s="5" t="s">
         <v>703</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>704</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M37" s="9"/>
       <c r="N37" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="O37" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="O37" s="4" t="s">
+    </row>
+    <row r="38" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="4">
+        <v>23</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="J38" s="5" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="48" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="D38" s="4">
-        <v>5</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="K38" s="5" t="s">
         <v>707</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>708</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>710</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M38" s="9"/>
       <c r="N38" s="4" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>504</v>
+        <v>635</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D39" s="4">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>714</v>
+        <v>680</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>715</v>
+        <v>681</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>73</v>
+        <v>515</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>716</v>
+        <v>692</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M39" s="9"/>
       <c r="N39" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="4">
+        <v>9</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="O39" s="4" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="64" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="4">
-        <v>102</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>722</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>727</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M40" s="9"/>
       <c r="N40" s="4" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>578</v>
+        <v>635</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>513</v>
+        <v>722</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D41" s="4">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G41" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="K41" s="5" t="s">
         <v>724</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>731</v>
       </c>
       <c r="L41" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M41" s="9"/>
       <c r="N41" s="4" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>734</v>
+        <v>635</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D42" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>227</v>
+        <v>715</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>226</v>
+        <v>716</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="L42" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M42" s="9"/>
       <c r="N42" s="4" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="4">
+        <v>17</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="K43" s="5" t="s">
         <v>734</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="4">
-        <v>97</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>743</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M43" s="9"/>
       <c r="N43" s="4" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>734</v>
+        <v>635</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>545</v>
+        <v>58</v>
       </c>
       <c r="D44" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>747</v>
+        <v>515</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>748</v>
+        <v>717</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M44" s="9"/>
       <c r="N44" s="4" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>734</v>
+        <v>635</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+        <v>742</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="4">
+        <v>23</v>
+      </c>
       <c r="E45" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="F45" s="4"/>
+        <v>715</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="G45" s="4" t="s">
-        <v>682</v>
+        <v>716</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>755</v>
+        <v>515</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="J45" s="5"/>
+        <v>717</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>743</v>
+      </c>
       <c r="K45" s="5" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M45" s="9"/>
       <c r="N45" s="4" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>734</v>
+        <v>635</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>584</v>
+        <v>58</v>
+      </c>
+      <c r="D46" s="4">
+        <v>26</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>760</v>
+        <v>715</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>610</v>
+        <v>716</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>34</v>
+        <v>515</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M46" s="9"/>
       <c r="N46" s="4" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>766</v>
+        <v>727</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D47" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>608</v>
+        <v>752</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>610</v>
+        <v>753</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>567</v>
+        <v>34</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M47" s="9"/>
       <c r="N47" s="4" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>771</v>
+        <v>727</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>772</v>
+        <v>58</v>
+      </c>
+      <c r="D48" s="4">
+        <v>14</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>65</v>
+        <v>752</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>610</v>
+        <v>753</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>586</v>
+        <v>758</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>761</v>
+        <v>717</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M48" s="9"/>
       <c r="N48" s="4" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>777</v>
+        <v>504</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>778</v>
+        <v>727</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>779</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>780</v>
+        <v>58</v>
+      </c>
+      <c r="D49" s="4">
+        <v>14</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>781</v>
+        <v>752</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>182</v>
+        <v>753</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>498</v>
+        <v>57</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>782</v>
+        <v>717</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M49" s="9"/>
       <c r="N49" s="4" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>777</v>
+        <v>504</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>787</v>
+        <v>727</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>788</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>789</v>
+        <v>58</v>
+      </c>
+      <c r="D50" s="4">
+        <v>14</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>790</v>
+        <v>752</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>791</v>
+        <v>753</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>83</v>
+        <v>767</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>792</v>
+        <v>717</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>793</v>
+        <v>768</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>38</v>
       </c>
       <c r="M50" s="9"/>
       <c r="N50" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" s="4">
+        <v>9</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M51" s="9"/>
+      <c r="N51" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" s="4">
+        <v>11</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="L52" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M52" s="9"/>
+      <c r="N52" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="4">
+        <v>97</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M53" s="9"/>
+      <c r="N53" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M54" s="9"/>
+      <c r="N54" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="4">
+        <v>8</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="K55" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="O50" s="4" t="s">
+      <c r="L55" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M55" s="9"/>
+      <c r="N55" s="4" t="s">
         <v>796</v>
       </c>
+      <c r="O55" s="4" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="4">
+        <v>102</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M56" s="9"/>
+      <c r="N56" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="4">
+        <v>97</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="9"/>
+      <c r="N57" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" s="4">
+        <v>9</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M58" s="9"/>
+      <c r="N58" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" s="4">
+        <v>97</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M59" s="9"/>
+      <c r="N59" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M60" s="9"/>
+      <c r="N60" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M61" s="9"/>
+      <c r="N61" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M62" s="9"/>
+      <c r="N62" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M63" s="9"/>
+      <c r="N63" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M64" s="9"/>
+      <c r="N64" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M65" s="9"/>
+      <c r="N65" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>867</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M50" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <conditionalFormatting sqref="A3:M50">
+  <autoFilter ref="A2:M65" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <conditionalFormatting sqref="A3:M65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$L3="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="L3:L50" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L3:L65" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"ja"</formula1>
     </dataValidation>
   </dataValidations>
